--- a/PTBR/Lang/PTBR/Dialog/Drama/felmera.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/felmera.xlsx
@@ -459,9 +459,8 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A arte não é, claro, uma explosão! Ela reside nos delicados movimentos do pincel, na tinta que seca silenciosamente e no olhar suave do observador. Ah, as pessoas esnobes desta cidade nunca entenderão isso, nem em uma vida inteira._x000D_
-_x000D_
-O mundo da arte mudou por causa de Jorg. Agora, a arte que não 'vende' é considerada inútil, e os pintores são forçados a criar pinturas vulgares, ditadas por tendências. A era de Lumiest acabou.</t>
+          <t>Arte não é, claro, uma explosão! Está nos movimentos delicados do pincel, na tinta que seca em silêncio e no olhar suave de quem contempla. Ai de mim, os esnobes desta cidade jamais entenderão, nem em uma vida.
+O mundo da arte mudou por causa de Jorg. Agora, arte que não 'vende' é tida como sem valor, e os pintores são forçados a pintar retratos vulgares movidos pela tendência. A era de Lumiest acabou.</t>
         </is>
       </c>
     </row>
@@ -499,7 +498,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Preciso que você pinte algo.</t>
+          <t>Preciso que pinte algo.</t>
         </is>
       </c>
     </row>
@@ -529,7 +528,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Preciso que você avalie uma pintura antiga.</t>
+          <t>Preciso que avalie uma pintura antiga.</t>
         </is>
       </c>
     </row>
@@ -586,7 +585,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Encontre outro pintor. Decidi largar meu pincel... pelo menos até que Jorg se retire do mundo da arte. Aquele homem mudou desde que se tornou o chefe da guilda.</t>
+          <t>Procure outro pintor. Decidi depositar meu pincel... pelo menos até Jorg se retirar do mundo da arte. Aquele homem mudou desde que virou o chefe da guilda.</t>
         </is>
       </c>
     </row>
@@ -621,7 +620,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Uma avaliação de uma pintura antiga... bem, isso pode de fato despertar um pouco meu interesse. Pois na arte do passado, sinto algo que ainda agita a paixão adormecida do pintor em mim.</t>
+          <t>Avaliar uma pintura antiga... bem, isso de fato desperta meu interesse um pouco. Porque na arte antiga sinto algo que ainda mexe com a paixão dormente do pintor em mim.</t>
         </is>
       </c>
     </row>
@@ -687,7 +686,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Se encontrar um esboço antigo, traga para mim. Talvez eu possa ajudar.</t>
+          <t>Se achar um esboço antigo, traga até mim. Talvez eu possa ajudar.</t>
         </is>
       </c>
     </row>
@@ -721,7 +720,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Certo, vou avaliar o esboço que você trouxe. Espere aqui, isso não vai demorar.  </t>
+          <t>Beleza, avaliarei o esboço que você tem. Espere aqui, não vai demorar.</t>
         </is>
       </c>
     </row>
@@ -758,7 +757,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Hmm, não é ruim, mas... Infelizmente, não há nenhuma pintura particularmente notável. Se encontrar outra pintura antiga, traga para mim.  </t>
+          <t>...Hum, não é mau, mas... Infelizmente, não há pintura particularmente notável. Se achar outra pintura antiga, traga até mim.</t>
         </is>
       </c>
     </row>
@@ -796,9 +795,9 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">...O que é isso!  
-Parece a obra de um pintor anônimo, mas que sensação é essa abalando minha alma?  
-Isto é... uma peça especial. Vou numerá-la pessoalmente. Guarde-a com cuidado nesse diário que você está carregando.  </t>
+          <t>...Que é isto!
+Parece a obra de um pintor anônimo, mas que é esta sensação que sacode minha alma?
+Esta é... uma peça especial. Vou numerá-la pessoalmente. Guarde-a com cuidado naquele diário que você carrega.</t>
         </is>
       </c>
     </row>
@@ -854,11 +853,9 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">...O que é isso!  _x000D_
-_x000D_
-Onde você encontrou uma coleção tão rara de pinturas? Não, isso não importa. Minha alma está tremendo de empolgação!  _x000D_
-_x000D_
-Vou numerar essas pinturas pessoalmente. Guarde-as com cuidado nesse diário que você está carregando.  </t>
+          <t>...Que é isto!
+Onde no mundo você achou uma coleção de pinturas raras dessas? Não, não importa. Minha alma neste momento estremece de empolgação!
+Numerarei estas pinturas pessoalmente. Guarde-as com cuidado naquele diário que você carrega.</t>
         </is>
       </c>
     </row>
@@ -904,7 +901,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por favor, aceite isto. Hehe, ao lembrar dos incontáveis esboços sem nome que você me mostrou, simplesmente não resisti a capturá-los na tela!  </t>
+          <t>Aceite isto. Hehe, lembrando dos incontáveis esboços sem nome que você me mostrou, simplesmente não pude resistir a capturá-los em tela!</t>
         </is>
       </c>
     </row>
